--- a/results/03-2026/beta/contributions-comparison-03-2026.xlsx
+++ b/results/03-2026/beta/contributions-comparison-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t xml:space="preserve">fiscal_impact_4q_ma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taxes_breakdown_contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transfers_breakdown_contribution</t>
   </si>
   <si>
     <t xml:space="preserve">2020 Q1</t>
@@ -631,13 +637,19 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -725,14 +737,20 @@
       </c>
       <c r="AE2" t="n">
         <v>0.577601160588483</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.0917203334476128</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.133565386955577</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -820,14 +838,20 @@
       </c>
       <c r="AE3" t="n">
         <v>3.00961320689186</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.218260041490563</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>8.62039918521447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -915,14 +939,20 @@
       </c>
       <c r="AE4" t="n">
         <v>3.83799587371516</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.552346472186169</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.96184053113914</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -1010,14 +1040,20 @@
       </c>
       <c r="AE5" t="n">
         <v>2.90763406238303</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.568772712361355</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-2.48939682148616</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -1105,14 +1141,20 @@
       </c>
       <c r="AE6" t="n">
         <v>4.92390395761885</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.193345941150108</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.80632121184456</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -1200,14 +1242,20 @@
       </c>
       <c r="AE7" t="n">
         <v>1.71389535669892</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.24689103402653</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.07983609284451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -1295,14 +1343,20 @@
       </c>
       <c r="AE8" t="n">
         <v>-0.106007963281536</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.31515314337929</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-2.09021198351942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -1390,14 +1444,20 @@
       </c>
       <c r="AE9" t="n">
         <v>-0.0643244424293917</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.208789857580898</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-2.44671974554818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -1485,14 +1545,20 @@
       </c>
       <c r="AE10" t="n">
         <v>-3.19423837869211</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.876075859460641</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-2.18229105712882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -1580,14 +1646,20 @@
       </c>
       <c r="AE11" t="n">
         <v>-3.83451695668526</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-1.20568398792863</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-3.10254365284433</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -1675,14 +1747,20 @@
       </c>
       <c r="AE12" t="n">
         <v>-3.62581383024339</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.657494577538429</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.71450742085577</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -1770,14 +1848,20 @@
       </c>
       <c r="AE13" t="n">
         <v>-2.98274687443948</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.332348599335242</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.443743756909895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -1865,14 +1949,20 @@
       </c>
       <c r="AE14" t="n">
         <v>-2.02726920885071</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.46615754920793</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-1.24231811101493</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -1960,14 +2050,20 @@
       </c>
       <c r="AE15" t="n">
         <v>-0.89685239280325</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.528053936044742</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.38247728801657</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -2055,14 +2151,20 @@
       </c>
       <c r="AE16" t="n">
         <v>-0.271579396961083</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.18171700258577</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.657570272399199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -2150,14 +2252,20 @@
       </c>
       <c r="AE17" t="n">
         <v>-0.223361959702328</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0862390375637294</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.663214681106842</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -2245,14 +2353,20 @@
       </c>
       <c r="AE18" t="n">
         <v>-0.140039015352823</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.659854636965577</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.455077977525216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -2340,14 +2454,20 @@
       </c>
       <c r="AE19" t="n">
         <v>0.048470906359604</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.508714905565415</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.384591213069866</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -2404,7 +2524,7 @@
         <v>-0.0440281009267043</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.055339761076515</v>
+        <v>-0.0553398426809612</v>
       </c>
       <c r="V20" t="n">
         <v>-0.0000481981319541984</v>
@@ -2425,24 +2545,30 @@
         <v>0.180384979214747</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.0742381544293124</v>
+        <v>-0.0742382360498926</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.106287009376921</v>
+        <v>0.106286927910456</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.601612110807237</v>
+        <v>0.601612029340773</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.186985184633372</v>
+        <v>0.186985164266756</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.274816107829201</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.0188983933689314</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -2499,7 +2625,7 @@
         <v>-0.0265684363093117</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0302912960815929</v>
+        <v>-0.0302912288977294</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0000584549268793934</v>
@@ -2520,24 +2646,30 @@
         <v>0.168699850674615</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.203974267353671</v>
+        <v>0.203974334374208</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.372316942334643</v>
+        <v>0.37231700923784</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.511324389373289</v>
+        <v>0.511324456276486</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.382038254203639</v>
+        <v>0.382038250562822</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.303037201695179</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.234265563271938</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -2594,7 +2726,7 @@
         <v>-0.0106418570513199</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0297652464367883</v>
+        <v>-0.0297652241785434</v>
       </c>
       <c r="V22" t="n">
         <v>-0.000305138334205149</v>
@@ -2615,24 +2747,30 @@
         <v>-0.0973949910447126</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.00437634796183327</v>
+        <v>-0.00437632570967921</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.101775840139854</v>
+        <v>-0.101775817864685</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.695053695338983</v>
+        <v>-0.695053673063814</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.165772303006992</v>
+        <v>0.165772304934967</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.0179122702725422</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.0253888984688642</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -2689,7 +2827,7 @@
         <v>-0.0100206453912311</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0233355697699924</v>
+        <v>-0.0233356501478242</v>
       </c>
       <c r="V23" t="n">
         <v>-0.00103802633880351</v>
@@ -2710,24 +2848,30 @@
         <v>-0.274529505412121</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.445899459268899</v>
+        <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.0273474449240554</v>
+        <v>-0.0273475251368821</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.433189323644773</v>
+        <v>-0.4331894038576</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.00382662970080774</v>
+        <v>-0.00382664782603897</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.491452879857937</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.469235029434092</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -2784,7 +2928,7 @@
         <v>-0.0086306387520275</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0297886168486114</v>
+        <v>-0.0297549970186519</v>
       </c>
       <c r="V24" t="n">
         <v>-0.0000539507371187338</v>
@@ -2805,24 +2949,30 @@
         <v>-0.139229581720164</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.400799604954009</v>
+        <v>0.400833075000047</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.262147478565033</v>
+        <v>0.262180996866793</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.260281409061421</v>
+        <v>0.26031492736318</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0891593051372617</v>
+        <v>-0.089150923320437</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.373161504158873</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.430588072018699</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -2879,7 +3029,7 @@
         <v>-0.00768147033983896</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0243002856780776</v>
+        <v>-0.0243055898647292</v>
       </c>
       <c r="V25" t="n">
         <v>-0.000053641022635247</v>
@@ -2900,24 +3050,30 @@
         <v>-0.246604197090628</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.359395773669213</v>
+        <v>0.359390490912369</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.113724678699862</v>
+        <v>0.113719382218795</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.23625881023253</v>
+        <v>-1.2362641067136</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.526055105038717</v>
+        <v>-0.526048064067958</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.389037106947415</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.383696080777098</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2926,7 +3082,7 @@
         <v>1.66203965967879</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.188444884734299</v>
+        <v>-10.958502461799</v>
       </c>
       <c r="F26" t="n">
         <v>-0.0884930148988476</v>
@@ -2974,7 +3130,7 @@
         <v>-0.00705294137280971</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0223732761489481</v>
+        <v>-0.0223752480478402</v>
       </c>
       <c r="V26" t="n">
         <v>-0.000508719097945849</v>
@@ -2986,33 +3142,39 @@
         <v>0.0459340379109913</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.61105778904093</v>
+        <v>0.0781758139260642</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.137463014096444</v>
+        <v>-9.37463861604627</v>
       </c>
       <c r="AA26" t="n">
         <v>0.258500252640078</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.334539830180878</v>
+        <v>0.334537865725155</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.652124840640011</v>
+        <v>0.65212288156191</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1257196155845</v>
+        <v>-8.6443399205583</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.179138222692154</v>
+        <v>-2.51336962594158</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.0572575248558411</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.356913113772995</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -3021,7 +3183,7 @@
         <v>-0.420442225197428</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.175941628331148</v>
+        <v>-0.0000851769538371798</v>
       </c>
       <c r="F27" t="n">
         <v>-0.0484841727550417</v>
@@ -3069,7 +3231,7 @@
         <v>-0.00646180404202451</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0205148231023012</v>
+        <v>-0.0205167048643551</v>
       </c>
       <c r="V27" t="n">
         <v>-0.000434592407571766</v>
@@ -3081,33 +3243,39 @@
         <v>0.0500663295646562</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.504761266635606</v>
+        <v>-0.503775436537204</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.09162258689297</v>
+        <v>0.0832480343859387</v>
       </c>
       <c r="AA27" t="n">
         <v>0.231146628054871</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.102373415401532</v>
+        <v>0.102371536071816</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.39327098033247</v>
+        <v>0.393269105575715</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.203112873196107</v>
+        <v>-0.0272582965755501</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.23665733530432</v>
+        <v>-2.41188684912107</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.0205269321072229</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.122888240936171</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
         <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3116,7 +3284,7 @@
         <v>-0.150762188480544</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.174802504544369</v>
+        <v>-0.000084879505190921</v>
       </c>
       <c r="F28" t="n">
         <v>-0.105484963636033</v>
@@ -3164,7 +3332,7 @@
         <v>-0.00574407026248544</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0194249836830286</v>
+        <v>-0.0194346552529259</v>
       </c>
       <c r="V28" t="n">
         <v>-0.000402363632723511</v>
@@ -3176,33 +3344,39 @@
         <v>-0.00902525902619576</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.18691079692726</v>
+        <v>-0.186873183932222</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.138653896097653</v>
+        <v>0.0360261159464873</v>
       </c>
       <c r="AA28" t="n">
         <v>0.00571655826186169</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.19452277010418</v>
+        <v>0.194513120390624</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.260227579794373</v>
+        <v>0.260217930663832</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.0653371132305395</v>
+        <v>0.109370862678097</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.15525270473133</v>
+        <v>-2.44962286529234</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.0722545818014097</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.21394777564355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -3211,7 +3385,7 @@
         <v>-0.110103309128598</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.198319979800335</v>
+        <v>-0.00137907822692901</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0898711501606448</v>
@@ -3259,7 +3433,7 @@
         <v>-0.00316614462247006</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.0123084447393558</v>
+        <v>-0.0123148070021903</v>
       </c>
       <c r="V29" t="n">
         <v>-0.000371323587931648</v>
@@ -3271,33 +3445,39 @@
         <v>-0.0362315364137063</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.169025391480398</v>
+        <v>-0.167623995548349</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.139397897448535</v>
+        <v>0.056141608192822</v>
       </c>
       <c r="AA29" t="n">
         <v>-0.107053821905824</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.179109120512849</v>
+        <v>0.179102771157839</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.132258518226359</v>
+        <v>0.132252161664947</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.176164770702574</v>
+        <v>0.02076977430942</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.420276214613819</v>
+        <v>-2.13536439503658</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.0547348704487144</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.191417578160029</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -3306,7 +3486,7 @@
         <v>-0.117417360335764</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.184699668516127</v>
+        <v>0.00187897068140066</v>
       </c>
       <c r="F30" t="n">
         <v>-0.341926351241659</v>
@@ -3354,7 +3534,7 @@
         <v>-0.00178043780722077</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.0116901087426907</v>
+        <v>-0.0116901955682493</v>
       </c>
       <c r="V30" t="n">
         <v>-0.000322751259010612</v>
@@ -3366,33 +3546,39 @@
         <v>-0.0191721781779693</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.163489049151569</v>
+        <v>-0.162650305358439</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.138627979700321</v>
+        <v>0.0471119157040758</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.564485461478001</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.109796463318841</v>
+        <v>0.109796376605536</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.394030419437947</v>
+        <v>-0.39403050667149</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.696147448289838</v>
+        <v>-0.509568896325853</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.285190551354765</v>
+        <v>-0.101671638978471</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.297470801393531</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.121486572173785</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -3401,7 +3587,7 @@
         <v>-0.100473963438391</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.179270880833719</v>
+        <v>0.00163362218100636</v>
       </c>
       <c r="F31" t="n">
         <v>-0.204786789431061</v>
@@ -3449,7 +3635,7 @@
         <v>-0.00149818167456064</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.00977296194688904</v>
+        <v>-0.00977454160018567</v>
       </c>
       <c r="V31" t="n">
         <v>-0.000315399360043053</v>
@@ -3461,33 +3647,39 @@
         <v>-0.0263285513735382</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.144849501312543</v>
+        <v>-0.144239404558048</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.134895342959567</v>
+        <v>0.0453990633006634</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.514519464576806</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0581216072125231</v>
+        <v>0.0581200287022978</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.396079368670447</v>
+        <v>-0.396080955831403</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.675824212942557</v>
+        <v>-0.494921297088788</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.403368386291377</v>
+        <v>-0.21858738910678</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.150504478130735</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.0678945703024835</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3496,7 +3688,7 @@
         <v>-0.107299968256074</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.18649358757554</v>
+        <v>-0.000933234579202482</v>
       </c>
       <c r="F32" t="n">
         <v>0.034233844104934</v>
@@ -3544,7 +3736,7 @@
         <v>-0.00123825675895601</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0249260452479259</v>
+        <v>0.0249199937637267</v>
       </c>
       <c r="V32" t="n">
         <v>-0.000309166722110859</v>
@@ -3556,33 +3748,39 @@
         <v>-0.0417236588915249</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.149995756965964</v>
+        <v>-0.14958715383456</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.14379779886565</v>
+        <v>0.0413539509992837</v>
       </c>
       <c r="AA32" t="n">
         <v>-0.298964935396437</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0255165371813811</v>
+        <v>0.0255104857351777</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.273367193246684</v>
+        <v>-0.273373263952081</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.567160749078297</v>
+        <v>-0.381606466787357</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.528824295253317</v>
+        <v>-0.341331721473144</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0876690554203386</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.000590491971451036</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3591,7 +3789,7 @@
         <v>-0.177189931468643</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.182994301623059</v>
+        <v>-0.0000601512990431544</v>
       </c>
       <c r="F33" t="n">
         <v>0.0724754946545994</v>
@@ -3651,10 +3849,10 @@
         <v>-0.0185165001078903</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.218468095965497</v>
+        <v>-0.218395145140965</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.141716137126205</v>
+        <v>0.0411450623732785</v>
       </c>
       <c r="AA33" t="n">
         <v>-0.288652119497053</v>
@@ -3666,10 +3864,16 @@
         <v>-0.287339460246776</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.647523693338478</v>
+        <v>-0.464589543014462</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.646664025912293</v>
+        <v>-0.462671550804114</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.140292342306064</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.0205292912419754</v>
       </c>
     </row>
   </sheetData>
@@ -3780,10 +3984,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -3875,10 +4079,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -3970,10 +4174,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -4065,10 +4269,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -4160,10 +4364,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -4255,10 +4459,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -4350,10 +4554,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -4445,10 +4649,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -4540,10 +4744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -4635,10 +4839,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -4730,10 +4934,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -4825,10 +5029,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -4920,10 +5124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -5015,10 +5219,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -5110,10 +5314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -5205,10 +5409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -5300,10 +5504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -5395,10 +5599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -5490,10 +5694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -5585,10 +5789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -5680,10 +5884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -5775,10 +5979,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -5870,10 +6074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -5965,10 +6169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -6060,10 +6264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -6155,10 +6359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -6250,10 +6454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
         <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -6345,10 +6549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -6440,10 +6644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -6535,10 +6739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -6630,10 +6834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -6725,10 +6929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -6926,7 +7130,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="n">
@@ -7019,7 +7223,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="n">
@@ -7112,7 +7316,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
@@ -7205,7 +7409,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
@@ -7298,7 +7502,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
@@ -7391,7 +7595,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
@@ -7484,7 +7688,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8"/>
       <c r="C8" t="n">
@@ -7577,7 +7781,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="n">
@@ -7670,7 +7874,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
@@ -7763,7 +7967,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11"/>
       <c r="C11" t="n">
@@ -7856,7 +8060,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12"/>
       <c r="C12" t="n">
@@ -7949,7 +8153,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13"/>
       <c r="C13" t="n">
@@ -8042,7 +8246,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14"/>
       <c r="C14" t="n">
@@ -8135,7 +8339,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15"/>
       <c r="C15" t="n">
@@ -8228,7 +8432,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16"/>
       <c r="C16" t="n">
@@ -8321,7 +8525,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
@@ -8414,7 +8618,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
@@ -8507,7 +8711,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
@@ -8600,7 +8804,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
@@ -8658,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0005073089037693</v>
+        <v>0.0005072272993231</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -8679,21 +8883,21 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.000507409166447398</v>
+        <v>0.000507327545867201</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.000506451145799003</v>
+        <v>0.000506369679334012</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.000506451145798947</v>
+        <v>0.000506369679334928</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.000126612786449987</v>
+        <v>0.000126592419833982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
@@ -8751,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.000439964626658199</v>
+        <v>0.000440031810521699</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -8772,21 +8976,21 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.000438895493497987</v>
+        <v>0.000438962514034996</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.000438126680630035</v>
+        <v>0.000438193583827018</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.000438126680629924</v>
+        <v>0.000438193583827018</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.000236144456607024</v>
+        <v>0.000236140815789987</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
@@ -8844,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.000379376992221101</v>
+        <v>0.000379399250466001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -8865,21 +9069,21 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.000379275296401639</v>
+        <v>0.0003792975485557</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.000379665382920003</v>
+        <v>0.000379687658089004</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.000379665382920003</v>
+        <v>0.000379687658088934</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.000331060802336997</v>
+        <v>0.000331062730311998</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23"/>
       <c r="C23" t="n">
@@ -8937,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.000402458356418799</v>
+        <v>0.000402377978586999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -8958,21 +9162,21 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.000400479289829003</v>
+        <v>0.000400399307197985</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.000401632143521301</v>
+        <v>0.000401551930694601</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.000401632143522013</v>
+        <v>0.000401551930694966</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0004314688382174</v>
+        <v>0.00043145071298617</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24"/>
       <c r="C24" t="n">
@@ -9030,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.000300958390987701</v>
+        <v>0.0003345782209472</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -9051,21 +9255,21 @@
         <v>-0.0394512618019685</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.000299617554382015</v>
+        <v>0.000333087600420001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.038987738436838</v>
+        <v>-0.038954220135078</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.038987738436838</v>
+        <v>-0.038954220135079</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.00944207855744179</v>
+        <v>-0.0094336967406171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25"/>
       <c r="C25" t="n">
@@ -9123,7 +9327,7 @@
         <v>0.0000199100317099798</v>
       </c>
       <c r="U25" t="n">
-        <v>0.000267699441200201</v>
+        <v>0.0002623952545486</v>
       </c>
       <c r="V25" t="n">
         <v>0.0000000454399653488993</v>
@@ -9144,21 +9348,21 @@
         <v>-0.039112611698256</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.039316578106324</v>
+        <v>-0.039321860863168</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.078364078174628</v>
+        <v>-0.078369374655695</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.20539059516562</v>
+        <v>-0.20539589164669</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.060899259019006</v>
+        <v>-0.060892218048247</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
@@ -9168,7 +9372,7 @@
         <v>0.23037891785822</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00000555421277900758</v>
+        <v>-10.7700520228519</v>
       </c>
       <c r="F26" t="n">
         <v>-0.00556818844149271</v>
@@ -9216,7 +9420,7 @@
         <v>-0.0000106613644118205</v>
       </c>
       <c r="U26" t="n">
-        <v>0.000250636444319798</v>
+        <v>0.000248664545427699</v>
       </c>
       <c r="V26" t="n">
         <v>-0.000000768973983820954</v>
@@ -9228,30 +9432,30 @@
         <v>-0.101610932193161</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2303384363526</v>
+        <v>-1.30254353876227</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.0000460357183970084</v>
+        <v>-9.23712956623143</v>
       </c>
       <c r="AA26" t="n">
         <v>-0.00250684460358203</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.134065677808519</v>
+        <v>-0.134067642264242</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.136192200140598</v>
+        <v>-0.136194159218699</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0941922719304</v>
+        <v>-10.6758672642124</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.037446107382136</v>
+        <v>-2.72995395601587</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
@@ -9261,7 +9465,7 @@
         <v>0.116705766473935</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000005185692580012</v>
+        <v>0.175861637069891</v>
       </c>
       <c r="F27" t="n">
         <v>-0.00442578860215821</v>
@@ -9309,7 +9513,7 @@
         <v>-0.00000976777056559044</v>
       </c>
       <c r="U27" t="n">
-        <v>0.000288399651173801</v>
+        <v>0.000286517889119899</v>
       </c>
       <c r="V27" t="n">
         <v>-0.000000656924759327032</v>
@@ -9321,30 +9525,30 @@
         <v>-0.105902904876044</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.116612229130245</v>
+        <v>0.117598059228647</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.0000987230362703984</v>
+        <v>0.174969344315179</v>
       </c>
       <c r="AA27" t="n">
         <v>-0.00140850019170102</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.154880934117271</v>
+        <v>-0.154882813446987</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.155908252177313</v>
+        <v>-0.155910126934068</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.039197300010799</v>
+        <v>0.136657276609758</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.047345840420717</v>
+        <v>-2.69589002484611</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
@@ -9354,7 +9558,7 @@
         <v>0.12082252119068</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00000515211811599747</v>
+        <v>0.174722777157294</v>
       </c>
       <c r="F28" t="n">
         <v>-0.012380994307307</v>
@@ -9402,7 +9606,7 @@
         <v>-0.00000868281344656042</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.000623417094314297</v>
+        <v>-0.000633088664211599</v>
       </c>
       <c r="V28" t="n">
         <v>-0.000000608208113365006</v>
@@ -9414,30 +9618,30 @@
         <v>-0.109342180463769</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.12080295524251</v>
+        <v>0.120840568237548</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.0000247180662850122</v>
+        <v>0.174704730110425</v>
       </c>
       <c r="AA28" t="n">
         <v>-0.010960801672402</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.175086239790481</v>
+        <v>-0.175095889504037</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.185993603253823</v>
+        <v>-0.186003252384364</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.0651659299450273</v>
+        <v>0.109542045963609</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.053890388297764</v>
+        <v>-2.65876595832143</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
@@ -9447,7 +9651,7 @@
         <v>-0.00203378662798</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00000584527071401109</v>
+        <v>0.19694674684412</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0122408655604479</v>
@@ -9495,7 +9699,7 @@
         <v>-0.00000478594808430008</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.000512921072305201</v>
+        <v>-0.000519283335139701</v>
       </c>
       <c r="V29" t="n">
         <v>-0.000000561288223580958</v>
@@ -9507,30 +9711,30 @@
         <v>-0.0896111834914301</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.002090479077238</v>
+        <v>-0.000689083145189007</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.0000625377199720001</v>
+        <v>0.195602043361329</v>
       </c>
       <c r="AA29" t="n">
         <v>-0.0110502737725877</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.150836443372386</v>
+        <v>-0.150842792727396</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.162019518863495</v>
+        <v>-0.162025875424907</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.16404746022076</v>
+        <v>0.0328870847912339</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.043554604561548</v>
+        <v>-2.59919521421195</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
@@ -9540,7 +9744,7 @@
         <v>-0.002168889011907</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000005443826508994</v>
+        <v>0.186584083024037</v>
       </c>
       <c r="F30" t="n">
         <v>-0.011121891178128</v>
@@ -9588,7 +9792,7 @@
         <v>-0.00000269130024095989</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.000498892890675</v>
+        <v>-0.0004989797162336</v>
       </c>
       <c r="V30" t="n">
         <v>-0.00000048786682059097</v>
@@ -9600,30 +9804,30 @@
         <v>-0.0503057049062374</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.002206162819993</v>
+        <v>-0.00136741902686299</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0000427176345959845</v>
+        <v>0.185782613038993</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.010281089298535</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.074004124531333</v>
+        <v>-0.074004211244638</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.084709851432065</v>
+        <v>-0.084709938665608</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.086873296617463</v>
+        <v>0.099705255346522</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.088820996698513</v>
+        <v>0.094697915677781</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
@@ -9633,7 +9837,7 @@
         <v>-0.00185591700120931</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00000528381875999906</v>
+        <v>0.180909786833485</v>
       </c>
       <c r="F31" t="n">
         <v>-0.010861640952474</v>
@@ -9681,7 +9885,7 @@
         <v>-0.00000226464145288005</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.00050400225756746</v>
+        <v>-0.00050558191086409</v>
       </c>
       <c r="V31" t="n">
         <v>-0.000000476753823247977</v>
@@ -9693,30 +9897,30 @@
         <v>-0.047567455831842</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.00189267685264102</v>
+        <v>-0.00128258009814602</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0000420436701919769</v>
+        <v>0.180336449930422</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.010175065866645</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.0647531997501999</v>
+        <v>-0.0647547782604252</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.075270271541633</v>
+        <v>-0.075271858702589</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.0771209047240821</v>
+        <v>0.103782011129687</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.098301897876833</v>
+        <v>0.086479099307764</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
@@ -9726,7 +9930,7 @@
         <v>-0.001982004377062</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00000549670036800731</v>
+        <v>0.185565849696706</v>
       </c>
       <c r="F32" t="n">
         <v>0.0063803013976292</v>
@@ -9774,7 +9978,7 @@
         <v>-0.00000187173916984</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.000251172998237299</v>
+        <v>-0.000257224482436497</v>
       </c>
       <c r="V32" t="n">
         <v>-0.000000467332680723011</v>
@@ -9786,30 +9990,30 @@
         <v>-0.0456112797006824</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.00201823858883901</v>
+        <v>-0.001609635457435</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0000417309121449883</v>
+        <v>0.185193480777079</v>
       </c>
       <c r="AA32" t="n">
         <v>0.007079270473967</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.0551168149014971</v>
+        <v>-0.0551228663477005</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.048219210904946</v>
+        <v>-0.048225281610343</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.0501957185816391</v>
+        <v>0.135358563709301</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.094559345035987</v>
+        <v>0.092933228744186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
@@ -9819,7 +10023,7 @@
         <v>-0.00327298530885001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00000539356263201674</v>
+        <v>0.182939543886648</v>
       </c>
       <c r="F33" t="n">
         <v>0.0074867235382082</v>
@@ -9879,10 +10083,10 @@
         <v>-0.0033013251817815</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.003308744728832</v>
+        <v>-0.00323579390430001</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0000411529826149781</v>
+        <v>0.182902352482098</v>
       </c>
       <c r="AA33" t="n">
         <v>0.00821343345686798</v>
@@ -9894,10 +10098,10 @@
         <v>-0.0000621865836839541</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.003329778329901</v>
+        <v>0.179604371994115</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.054379924563272</v>
+        <v>0.129612550544907</v>
       </c>
     </row>
   </sheetData>
